--- a/research/traditional_assets/database/data/australia/australia_semiconductor.xlsx
+++ b/research/traditional_assets/database/data/australia/australia_semiconductor.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ6"/>
+  <dimension ref="A1:AQ5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,25 +588,25 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.00415</v>
+        <v>0.202</v>
       </c>
       <c r="G2">
-        <v>-1.407355021216407</v>
+        <v>-1.834601131265847</v>
       </c>
       <c r="H2">
-        <v>-2.397454031117397</v>
+        <v>-2.863272869124244</v>
       </c>
       <c r="I2">
-        <v>-2.452263083451202</v>
+        <v>-2.904232494636239</v>
       </c>
       <c r="J2">
-        <v>-2.452263083451202</v>
+        <v>-2.904232494636239</v>
       </c>
       <c r="K2">
-        <v>-19.59</v>
+        <v>-20.89</v>
       </c>
       <c r="L2">
-        <v>-3.463578500707213</v>
+        <v>-4.074507509264677</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -630,73 +630,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>13.487</v>
+        <v>25.28</v>
       </c>
       <c r="V2">
-        <v>0.02688742249955144</v>
+        <v>0.0430811179277437</v>
       </c>
       <c r="W2">
-        <v>-1.492539388322521</v>
+        <v>-0.6852112676056339</v>
       </c>
       <c r="X2">
-        <v>0.07727403649189375</v>
+        <v>0.1379150503172686</v>
       </c>
       <c r="Y2">
-        <v>-1.569813424814415</v>
+        <v>-0.8231263179229025</v>
       </c>
       <c r="Z2">
-        <v>0.1760951461751611</v>
+        <v>0.2410437235543019</v>
       </c>
       <c r="AA2">
-        <v>-0.1850671559538754</v>
+        <v>-0.9274785160343744</v>
       </c>
       <c r="AB2">
-        <v>0.07722572359319804</v>
+        <v>0.1377685687919111</v>
       </c>
       <c r="AC2">
-        <v>-0.2622928795470735</v>
+        <v>-1.065284803766975</v>
       </c>
       <c r="AD2">
-        <v>2.014</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>2.014</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AG2">
-        <v>-11.473</v>
+        <v>-24.47</v>
       </c>
       <c r="AH2">
-        <v>0.003999015138277763</v>
+        <v>0.001378465308623067</v>
       </c>
       <c r="AI2">
-        <v>0.05883040252380674</v>
+        <v>0.01358148893360161</v>
       </c>
       <c r="AJ2">
-        <v>-0.02340774110095748</v>
+        <v>-0.04351537353511285</v>
       </c>
       <c r="AK2">
-        <v>-0.5529956138236853</v>
+        <v>-0.7121653084982539</v>
       </c>
       <c r="AL2">
-        <v>0.375</v>
+        <v>0.029</v>
       </c>
       <c r="AM2">
-        <v>0.26</v>
+        <v>-0.156</v>
       </c>
       <c r="AN2">
-        <v>-0.1485250737463127</v>
+        <v>-0.05517711171662126</v>
       </c>
       <c r="AO2">
-        <v>-36.98666666666666</v>
+        <v>-513.448275862069</v>
       </c>
       <c r="AP2">
-        <v>0.8460914454277285</v>
+        <v>1.666893732970028</v>
       </c>
       <c r="AQ2">
-        <v>-53.34615384615384</v>
+        <v>95.44871794871794</v>
       </c>
     </row>
     <row r="3">
@@ -707,7 +707,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>4DS Memory Limited (ASX:4DS)</t>
+          <t>Silex Systems Limited (ASX:SLX)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -716,25 +716,25 @@
         </is>
       </c>
       <c r="D3">
-        <v>-0.451</v>
+        <v>0.202</v>
       </c>
       <c r="G3">
-        <v>-347.9999999999999</v>
+        <v>-0.1387387387387387</v>
       </c>
       <c r="H3">
-        <v>-992</v>
+        <v>-0.331081081081081</v>
       </c>
       <c r="I3">
-        <v>-1008</v>
+        <v>-0.3536036036036036</v>
       </c>
       <c r="J3">
-        <v>-1008</v>
+        <v>-0.3536036036036036</v>
       </c>
       <c r="K3">
-        <v>-4.99</v>
+        <v>-6.52</v>
       </c>
       <c r="L3">
-        <v>-998</v>
+        <v>-1.468468468468468</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -758,73 +758,73 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>3.22</v>
+        <v>3.47</v>
       </c>
       <c r="V3">
-        <v>0.03326446280991736</v>
+        <v>0.007771556550951848</v>
       </c>
       <c r="W3">
-        <v>-4.455357142857142</v>
+        <v>-0.3951515151515151</v>
       </c>
       <c r="X3">
-        <v>0.07731453741040512</v>
+        <v>0.1379150503172686</v>
       </c>
       <c r="Y3">
-        <v>-4.532671680267548</v>
+        <v>-0.5330665654687837</v>
       </c>
       <c r="Z3">
-        <v>-0.02336448598130841</v>
+        <v>0.3785811732605731</v>
       </c>
       <c r="AA3">
-        <v>23.55140186915888</v>
+        <v>-0.1338676671214188</v>
       </c>
       <c r="AB3">
-        <v>0.0772033163771929</v>
+        <v>0.1377685687919111</v>
       </c>
       <c r="AC3">
-        <v>23.47419855278169</v>
+        <v>-0.2716362359133299</v>
       </c>
       <c r="AD3">
-        <v>0.194</v>
+        <v>0.677</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>0.194</v>
+        <v>0.677</v>
       </c>
       <c r="AG3">
-        <v>-3.026</v>
+        <v>-2.793</v>
       </c>
       <c r="AH3">
-        <v>0.002000123718992928</v>
+        <v>0.001513941906672302</v>
       </c>
       <c r="AI3">
-        <v>0.06150919467343056</v>
+        <v>0.01908278603038589</v>
       </c>
       <c r="AJ3">
-        <v>-0.03226907245078593</v>
+        <v>-0.006294694471802339</v>
       </c>
       <c r="AK3">
-        <v>45.84848484848466</v>
+        <v>-0.08726216140219328</v>
       </c>
       <c r="AL3">
-        <v>0.016</v>
+        <v>0.014</v>
       </c>
       <c r="AM3">
-        <v>0.016</v>
+        <v>-0.109</v>
       </c>
       <c r="AN3">
-        <v>-0.03911290322580645</v>
+        <v>-0.4605442176870749</v>
       </c>
       <c r="AO3">
-        <v>-315</v>
+        <v>-112.1428571428571</v>
       </c>
       <c r="AP3">
-        <v>0.6100806451612903</v>
+        <v>1.9</v>
       </c>
       <c r="AQ3">
-        <v>-315</v>
+        <v>14.40366972477064</v>
       </c>
     </row>
     <row r="4">
@@ -844,25 +844,25 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.486</v>
+        <v>0.723</v>
       </c>
       <c r="G4">
-        <v>-3.21937321937322</v>
+        <v>-10.83582089552239</v>
       </c>
       <c r="H4">
-        <v>-5.2991452991453</v>
+        <v>-13.16417910447761</v>
       </c>
       <c r="I4">
-        <v>-5.356125356125356</v>
+        <v>-13.2089552238806</v>
       </c>
       <c r="J4">
-        <v>-5.356125356125356</v>
+        <v>-13.2089552238806</v>
       </c>
       <c r="K4">
-        <v>-4.94</v>
+        <v>-9.73</v>
       </c>
       <c r="L4">
-        <v>-14.07407407407408</v>
+        <v>-14.52238805970149</v>
       </c>
       <c r="M4">
         <v>-0</v>
@@ -886,70 +886,70 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>4.68</v>
+        <v>18.2</v>
       </c>
       <c r="V4">
-        <v>0.02311111111111111</v>
+        <v>0.1748318924111431</v>
       </c>
       <c r="W4">
-        <v>-0.2923076923076924</v>
+        <v>-0.6852112676056339</v>
       </c>
       <c r="X4">
-        <v>0.07723210412083963</v>
+        <v>0.1378192853121226</v>
       </c>
       <c r="Y4">
-        <v>-0.369539796428532</v>
+        <v>-0.8230305529177565</v>
       </c>
       <c r="Z4">
-        <v>0.03106194690265487</v>
+        <v>0.07021588765457976</v>
       </c>
       <c r="AA4">
-        <v>-0.1663716814159292</v>
+        <v>-0.9274785160343744</v>
       </c>
       <c r="AB4">
-        <v>0.07722607246918302</v>
+        <v>0.1378062877326005</v>
       </c>
       <c r="AC4">
-        <v>-0.2435977538851122</v>
+        <v>-1.065284803766975</v>
       </c>
       <c r="AD4">
-        <v>0.022</v>
+        <v>0.014</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>0.022</v>
+        <v>0.014</v>
       </c>
       <c r="AG4">
-        <v>-4.657999999999999</v>
+        <v>-18.186</v>
       </c>
       <c r="AH4">
-        <v>0.0001086301735120135</v>
+        <v>0.0001344679870142344</v>
       </c>
       <c r="AI4">
-        <v>0.001546899170299536</v>
+        <v>0.0006891798759476223</v>
       </c>
       <c r="AJ4">
-        <v>-0.02354404019368991</v>
+        <v>-0.2116767930721419</v>
       </c>
       <c r="AK4">
-        <v>-0.4881576189478096</v>
+        <v>-8.602649006622514</v>
       </c>
       <c r="AL4">
         <v>0</v>
       </c>
       <c r="AM4">
-        <v>-0.008</v>
+        <v>-0.059</v>
       </c>
       <c r="AN4">
-        <v>-0.01182795698924731</v>
+        <v>-0.001587301587301587</v>
       </c>
       <c r="AP4">
-        <v>2.504301075268817</v>
+        <v>2.061904761904762</v>
       </c>
       <c r="AQ4">
-        <v>235</v>
+        <v>150</v>
       </c>
     </row>
     <row r="5">
@@ -960,7 +960,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Silex Systems Limited (ASX:SLX)</t>
+          <t>4DS Memory Limited (ASX:4DS)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -969,25 +969,25 @@
         </is>
       </c>
       <c r="D5">
-        <v>0.00415</v>
+        <v>-0.194</v>
       </c>
       <c r="G5">
-        <v>-0.8127659574468086</v>
+        <v>-89.99999999999999</v>
       </c>
       <c r="H5">
-        <v>-1.514893617021277</v>
+        <v>-258.235294117647</v>
       </c>
       <c r="I5">
-        <v>-1.553191489361702</v>
+        <v>-262.9411764705882</v>
       </c>
       <c r="J5">
-        <v>-1.553191489361702</v>
+        <v>-262.9411764705882</v>
       </c>
       <c r="K5">
-        <v>-5.19</v>
+        <v>-4.64</v>
       </c>
       <c r="L5">
-        <v>-2.208510638297872</v>
+        <v>-272.9411764705882</v>
       </c>
       <c r="M5">
         <v>-0</v>
@@ -1011,198 +1011,64 @@
         <v>0</v>
       </c>
       <c r="U5">
-        <v>4.8</v>
+        <v>3.61</v>
       </c>
       <c r="V5">
-        <v>0.02426693629929221</v>
+        <v>0.09972375690607733</v>
       </c>
       <c r="W5">
-        <v>-0.2731578947368421</v>
+        <v>-1.567567567567568</v>
       </c>
       <c r="X5">
-        <v>0.07723353557338239</v>
+        <v>0.138037796810938</v>
       </c>
       <c r="Y5">
-        <v>-0.3503914303102245</v>
-      </c>
-      <c r="Z5">
-        <v>0.1311896388098029</v>
-      </c>
-      <c r="AA5">
-        <v>-0.2037626304918216</v>
+        <v>-1.705605364378506</v>
       </c>
       <c r="AB5">
-        <v>0.07722537471721307</v>
-      </c>
-      <c r="AC5">
-        <v>-0.2809880052090347</v>
+        <v>0.1377462918735636</v>
       </c>
       <c r="AD5">
-        <v>0.028</v>
+        <v>0.119</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>0.028</v>
+        <v>0.119</v>
       </c>
       <c r="AG5">
-        <v>-4.772</v>
+        <v>-3.491</v>
       </c>
       <c r="AH5">
-        <v>0.0001415370928281133</v>
+        <v>0.003276521930669897</v>
       </c>
       <c r="AI5">
-        <v>0.001694094869312682</v>
+        <v>0.03091712133021564</v>
       </c>
       <c r="AJ5">
-        <v>-0.02472180201836003</v>
+        <v>-0.1067290348222202</v>
       </c>
       <c r="AK5">
-        <v>-0.4068894952251024</v>
+        <v>-14.60669456066944</v>
       </c>
       <c r="AL5">
-        <v>0.001</v>
+        <v>0.015</v>
       </c>
       <c r="AM5">
-        <v>-0.106</v>
+        <v>0.012</v>
       </c>
       <c r="AN5">
-        <v>-0.007865168539325843</v>
+        <v>-0.02710706150341686</v>
       </c>
       <c r="AO5">
-        <v>-3650</v>
+        <v>-298</v>
       </c>
       <c r="AP5">
-        <v>1.340449438202247</v>
+        <v>0.7952164009111617</v>
       </c>
       <c r="AQ5">
-        <v>34.43396226415094</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Australia</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Sensera Limited (ASX:SE1)</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Semiconductor</t>
-        </is>
-      </c>
-      <c r="G6">
-        <v>-1.077966101694915</v>
-      </c>
-      <c r="H6">
-        <v>-1.077966101694915</v>
-      </c>
-      <c r="I6">
-        <v>-1.11864406779661</v>
-      </c>
-      <c r="J6">
-        <v>-1.11864406779661</v>
-      </c>
-      <c r="K6">
-        <v>-4.47</v>
-      </c>
-      <c r="L6">
-        <v>-1.515254237288135</v>
-      </c>
-      <c r="M6">
-        <v>-0</v>
-      </c>
-      <c r="N6">
-        <v>-0</v>
-      </c>
-      <c r="O6">
-        <v>0</v>
-      </c>
-      <c r="P6">
-        <v>-0</v>
-      </c>
-      <c r="Q6">
-        <v>-0</v>
-      </c>
-      <c r="R6">
-        <v>0</v>
-      </c>
-      <c r="S6">
-        <v>0</v>
-      </c>
-      <c r="U6">
-        <v>0.787</v>
-      </c>
-      <c r="V6">
-        <v>0.1745011086474501</v>
-      </c>
-      <c r="W6">
-        <v>-2.69277108433735</v>
-      </c>
-      <c r="X6">
-        <v>0.09429518935910478</v>
-      </c>
-      <c r="Y6">
-        <v>-2.787066273696454</v>
-      </c>
-      <c r="Z6">
-        <v>0.9455128205128208</v>
-      </c>
-      <c r="AA6">
-        <v>-1.057692307692308</v>
-      </c>
-      <c r="AB6">
-        <v>0.08603988210016891</v>
-      </c>
-      <c r="AC6">
-        <v>-1.143732189792477</v>
-      </c>
-      <c r="AD6">
-        <v>1.77</v>
-      </c>
-      <c r="AE6">
-        <v>0</v>
-      </c>
-      <c r="AF6">
-        <v>1.77</v>
-      </c>
-      <c r="AG6">
-        <v>0.983</v>
-      </c>
-      <c r="AH6">
-        <v>0.2818471337579618</v>
-      </c>
-      <c r="AI6">
-        <v>5.363636363636362</v>
-      </c>
-      <c r="AJ6">
-        <v>0.1789550336792281</v>
-      </c>
-      <c r="AK6">
-        <v>-2.150984682713348</v>
-      </c>
-      <c r="AL6">
-        <v>0.358</v>
-      </c>
-      <c r="AM6">
-        <v>0.358</v>
-      </c>
-      <c r="AN6">
-        <v>-0.5566037735849056</v>
-      </c>
-      <c r="AO6">
-        <v>-9.217877094972067</v>
-      </c>
-      <c r="AP6">
-        <v>-0.3091194968553459</v>
-      </c>
-      <c r="AQ6">
-        <v>-9.217877094972067</v>
+        <v>-372.4999999999999</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/australia/australia_semiconductor.xlsx
+++ b/research/traditional_assets/database/data/australia/australia_semiconductor.xlsx
@@ -588,25 +588,25 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.202</v>
+        <v>0.586</v>
       </c>
       <c r="G2">
-        <v>-1.834601131265847</v>
+        <v>-14.01203610832498</v>
       </c>
       <c r="H2">
-        <v>-2.863272869124244</v>
+        <v>-36.16850551654965</v>
       </c>
       <c r="I2">
-        <v>-2.904232494636239</v>
+        <v>-36.46940822467402</v>
       </c>
       <c r="J2">
-        <v>-2.904232494636239</v>
+        <v>-36.46940822467402</v>
       </c>
       <c r="K2">
-        <v>-20.89</v>
+        <v>-35.88</v>
       </c>
       <c r="L2">
-        <v>-4.074507509264677</v>
+        <v>-35.98796389167503</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -630,73 +630,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>25.28</v>
+        <v>62.744</v>
       </c>
       <c r="V2">
-        <v>0.0430811179277437</v>
+        <v>0.08764352563207152</v>
       </c>
       <c r="W2">
-        <v>-0.6852112676056339</v>
+        <v>-0.6860158311345647</v>
       </c>
       <c r="X2">
-        <v>0.1379150503172686</v>
+        <v>0.1149779515346299</v>
       </c>
       <c r="Y2">
-        <v>-0.8231263179229025</v>
+        <v>-0.8009937826691945</v>
       </c>
       <c r="Z2">
-        <v>0.2410437235543019</v>
+        <v>0.04304650058287639</v>
       </c>
       <c r="AA2">
-        <v>-0.9274785160343744</v>
+        <v>-7.473508087005023</v>
       </c>
       <c r="AB2">
-        <v>0.1377685687919111</v>
+        <v>0.11495707941506</v>
       </c>
       <c r="AC2">
-        <v>-1.065284803766975</v>
+        <v>-7.588459144113546</v>
       </c>
       <c r="AD2">
-        <v>0.8100000000000001</v>
+        <v>0.232</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>0.8100000000000001</v>
+        <v>0.232</v>
       </c>
       <c r="AG2">
-        <v>-24.47</v>
+        <v>-62.512</v>
       </c>
       <c r="AH2">
-        <v>0.001378465308623067</v>
+        <v>0.0003239626214161635</v>
       </c>
       <c r="AI2">
-        <v>0.01358148893360161</v>
+        <v>0.002985766132145891</v>
       </c>
       <c r="AJ2">
-        <v>-0.04351537353511285</v>
+        <v>-0.09567362730873541</v>
       </c>
       <c r="AK2">
-        <v>-0.7121653084982539</v>
+        <v>-4.179168338013104</v>
       </c>
       <c r="AL2">
-        <v>0.029</v>
+        <v>0.007</v>
       </c>
       <c r="AM2">
-        <v>-0.156</v>
+        <v>-1.309</v>
       </c>
       <c r="AN2">
-        <v>-0.05517711171662126</v>
+        <v>-0.006433721575152524</v>
       </c>
       <c r="AO2">
-        <v>-513.448275862069</v>
+        <v>-5194.285714285714</v>
       </c>
       <c r="AP2">
-        <v>1.666893732970028</v>
+        <v>1.733555185801442</v>
       </c>
       <c r="AQ2">
-        <v>95.44871794871794</v>
+        <v>27.77692895339954</v>
       </c>
     </row>
     <row r="3">
@@ -707,7 +707,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Silex Systems Limited (ASX:SLX)</t>
+          <t>Archer Materials Limited (ASX:AXE)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -716,25 +716,25 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.202</v>
+        <v>0.586</v>
       </c>
       <c r="G3">
-        <v>-0.1387387387387387</v>
+        <v>-3.801404212637914</v>
       </c>
       <c r="H3">
-        <v>-0.331081081081081</v>
+        <v>-5.777331995987963</v>
       </c>
       <c r="I3">
-        <v>-0.3536036036036036</v>
+        <v>-5.817452357071214</v>
       </c>
       <c r="J3">
-        <v>-0.3536036036036036</v>
+        <v>-5.817452357071214</v>
       </c>
       <c r="K3">
-        <v>-6.52</v>
+        <v>-6.02</v>
       </c>
       <c r="L3">
-        <v>-1.468468468468468</v>
+        <v>-6.038114343029087</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -758,73 +758,70 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>3.47</v>
+        <v>0.514</v>
       </c>
       <c r="V3">
-        <v>0.007771556550951848</v>
+        <v>0.007787878787878788</v>
       </c>
       <c r="W3">
-        <v>-0.3951515151515151</v>
+        <v>-0.296551724137931</v>
       </c>
       <c r="X3">
-        <v>0.1379150503172686</v>
+        <v>0.1149642938313704</v>
       </c>
       <c r="Y3">
-        <v>-0.5330665654687837</v>
+        <v>-0.4115160179693015</v>
       </c>
       <c r="Z3">
-        <v>0.3785811732605731</v>
+        <v>0.05156185353744312</v>
       </c>
       <c r="AA3">
-        <v>-0.1338676671214188</v>
+        <v>-0.2999586263963591</v>
       </c>
       <c r="AB3">
-        <v>0.1377685687919111</v>
+        <v>0.11495707941506</v>
       </c>
       <c r="AC3">
-        <v>-0.2716362359133299</v>
+        <v>-0.4149157058114191</v>
       </c>
       <c r="AD3">
-        <v>0.677</v>
+        <v>0.006</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>0.677</v>
+        <v>0.006</v>
       </c>
       <c r="AG3">
-        <v>-2.793</v>
+        <v>-0.508</v>
       </c>
       <c r="AH3">
-        <v>0.001513941906672302</v>
+        <v>9.09008271975275e-05</v>
       </c>
       <c r="AI3">
-        <v>0.01908278603038589</v>
+        <v>0.0003467005662775916</v>
       </c>
       <c r="AJ3">
-        <v>-0.006294694471802339</v>
+        <v>-0.007756672570695657</v>
       </c>
       <c r="AK3">
-        <v>-0.08726216140219328</v>
+        <v>-0.03025250119104335</v>
       </c>
       <c r="AL3">
-        <v>0.014</v>
+        <v>0</v>
       </c>
       <c r="AM3">
-        <v>-0.109</v>
+        <v>-0.451</v>
       </c>
       <c r="AN3">
-        <v>-0.4605442176870749</v>
-      </c>
-      <c r="AO3">
-        <v>-112.1428571428571</v>
+        <v>-0.001041666666666667</v>
       </c>
       <c r="AP3">
-        <v>1.9</v>
+        <v>0.08819444444444445</v>
       </c>
       <c r="AQ3">
-        <v>14.40366972477064</v>
+        <v>12.86031042128603</v>
       </c>
     </row>
     <row r="4">
@@ -835,7 +832,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Archer Materials Limited (ASX:AXE)</t>
+          <t>Weebit Nano Limited (ASX:WBT)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -843,26 +840,8 @@
           <t>Semiconductor</t>
         </is>
       </c>
-      <c r="D4">
-        <v>0.723</v>
-      </c>
-      <c r="G4">
-        <v>-10.83582089552239</v>
-      </c>
-      <c r="H4">
-        <v>-13.16417910447761</v>
-      </c>
-      <c r="I4">
-        <v>-13.2089552238806</v>
-      </c>
-      <c r="J4">
-        <v>-13.2089552238806</v>
-      </c>
       <c r="K4">
-        <v>-9.73</v>
-      </c>
-      <c r="L4">
-        <v>-14.52238805970149</v>
+        <v>-26</v>
       </c>
       <c r="M4">
         <v>-0</v>
@@ -886,70 +865,70 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>18.2</v>
+        <v>58.5</v>
       </c>
       <c r="V4">
-        <v>0.1748318924111431</v>
+        <v>0.1068688344903179</v>
       </c>
       <c r="W4">
-        <v>-0.6852112676056339</v>
+        <v>-0.6860158311345647</v>
       </c>
       <c r="X4">
-        <v>0.1378192853121226</v>
+        <v>0.1149779515346299</v>
       </c>
       <c r="Y4">
-        <v>-0.8230305529177565</v>
+        <v>-0.8009937826691945</v>
       </c>
       <c r="Z4">
-        <v>0.07021588765457976</v>
+        <v>0</v>
       </c>
       <c r="AA4">
-        <v>-0.9274785160343744</v>
+        <v>-7.473508087005023</v>
       </c>
       <c r="AB4">
-        <v>0.1378062877326005</v>
+        <v>0.1149510571085235</v>
       </c>
       <c r="AC4">
-        <v>-1.065284803766975</v>
+        <v>-7.588459144113546</v>
       </c>
       <c r="AD4">
-        <v>0.014</v>
+        <v>0.19</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>0.014</v>
+        <v>0.19</v>
       </c>
       <c r="AG4">
-        <v>-18.186</v>
+        <v>-58.31</v>
       </c>
       <c r="AH4">
-        <v>0.0001344679870142344</v>
+        <v>0.0003469749264961011</v>
       </c>
       <c r="AI4">
-        <v>0.0006891798759476223</v>
+        <v>0.003357483654355893</v>
       </c>
       <c r="AJ4">
-        <v>-0.2116767930721419</v>
+        <v>-0.1192214111922141</v>
       </c>
       <c r="AK4">
-        <v>-8.602649006622514</v>
+        <v>30.52879581151827</v>
       </c>
       <c r="AL4">
         <v>0</v>
       </c>
       <c r="AM4">
-        <v>-0.059</v>
+        <v>-0.838</v>
       </c>
       <c r="AN4">
-        <v>-0.001587301587301587</v>
+        <v>-0.007142857142857143</v>
       </c>
       <c r="AP4">
-        <v>2.061904761904762</v>
+        <v>2.192105263157895</v>
       </c>
       <c r="AQ4">
-        <v>150</v>
+        <v>31.98090692124105</v>
       </c>
     </row>
     <row r="5">
@@ -968,26 +947,8 @@
           <t>Semiconductor</t>
         </is>
       </c>
-      <c r="D5">
-        <v>-0.194</v>
-      </c>
-      <c r="G5">
-        <v>-89.99999999999999</v>
-      </c>
-      <c r="H5">
-        <v>-258.235294117647</v>
-      </c>
-      <c r="I5">
-        <v>-262.9411764705882</v>
-      </c>
-      <c r="J5">
-        <v>-262.9411764705882</v>
-      </c>
       <c r="K5">
-        <v>-4.64</v>
-      </c>
-      <c r="L5">
-        <v>-272.9411764705882</v>
+        <v>-3.86</v>
       </c>
       <c r="M5">
         <v>-0</v>
@@ -1011,64 +972,73 @@
         <v>0</v>
       </c>
       <c r="U5">
-        <v>3.61</v>
+        <v>3.73</v>
       </c>
       <c r="V5">
-        <v>0.09972375690607733</v>
+        <v>0.03639024390243902</v>
       </c>
       <c r="W5">
-        <v>-1.567567567567568</v>
+        <v>-1.03485254691689</v>
       </c>
       <c r="X5">
-        <v>0.138037796810938</v>
+        <v>0.1149781713998424</v>
       </c>
       <c r="Y5">
-        <v>-1.705605364378506</v>
+        <v>-1.149830718316732</v>
+      </c>
+      <c r="Z5">
+        <v>0</v>
+      </c>
+      <c r="AA5">
+        <v>-15.73221757322174</v>
       </c>
       <c r="AB5">
-        <v>0.1377462918735636</v>
+        <v>0.11496021796524</v>
+      </c>
+      <c r="AC5">
+        <v>-15.84717779118698</v>
       </c>
       <c r="AD5">
-        <v>0.119</v>
+        <v>0.036</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>0.119</v>
+        <v>0.036</v>
       </c>
       <c r="AG5">
-        <v>-3.491</v>
+        <v>-3.694</v>
       </c>
       <c r="AH5">
-        <v>0.003276521930669897</v>
+        <v>0.0003510962003588983</v>
       </c>
       <c r="AI5">
-        <v>0.03091712133021564</v>
+        <v>0.009458749343142406</v>
       </c>
       <c r="AJ5">
-        <v>-0.1067290348222202</v>
+        <v>-0.03738639353885392</v>
       </c>
       <c r="AK5">
-        <v>-14.60669456066944</v>
+        <v>-48.60526315789469</v>
       </c>
       <c r="AL5">
-        <v>0.015</v>
+        <v>0.007</v>
       </c>
       <c r="AM5">
-        <v>0.012</v>
+        <v>-0.02</v>
       </c>
       <c r="AN5">
-        <v>-0.02710706150341686</v>
+        <v>-0.009729729729729729</v>
       </c>
       <c r="AO5">
-        <v>-298</v>
+        <v>-537.1428571428571</v>
       </c>
       <c r="AP5">
-        <v>0.7952164009111617</v>
+        <v>0.9983783783783783</v>
       </c>
       <c r="AQ5">
-        <v>-372.4999999999999</v>
+        <v>188</v>
       </c>
     </row>
   </sheetData>
